--- a/tuition.xlsx
+++ b/tuition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\CP\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6037E7F-72A0-4CE4-B6AF-A14CED2BA11B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D60FC4F3-E1A1-45BE-B228-EFCD79778249}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -243,10 +243,10 @@
     <t>17,500,000‎</t>
   </si>
   <si>
-    <t>8500,000‎</t>
-  </si>
-  <si>
     <t>250,000‎</t>
+  </si>
+  <si>
+    <t>8,500,000‎</t>
   </si>
 </sst>
 </file>
@@ -732,10 +732,10 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C9" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="D9" s="1" t="s">
         <v>37</v>
@@ -749,10 +749,10 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>72</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>37</v>
